--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\incoming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58167064-B411-445A-B49A-ABF585C3BA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D064E9-C4DC-428C-9EF1-5B14A02523F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="47">
   <si>
     <t>日付</t>
   </si>
@@ -1208,392 +1208,182 @@
       <c r="E35" s="5"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A36" s="6">
-        <v>45901</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36">
-        <v>662352</v>
-      </c>
+      <c r="A36" s="6"/>
+      <c r="B36" s="5"/>
       <c r="D36" s="7"/>
       <c r="E36" s="5"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A37" s="6">
-        <v>45902</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C37">
-        <v>319165</v>
-      </c>
+      <c r="A37" s="6"/>
+      <c r="B37" s="5"/>
       <c r="D37" s="7"/>
       <c r="E37" s="5"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A38" s="6">
-        <v>45903</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38">
-        <v>261618</v>
-      </c>
+      <c r="A38" s="6"/>
+      <c r="B38" s="5"/>
       <c r="D38" s="7"/>
       <c r="E38" s="5"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A39" s="6">
-        <v>45904</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C39">
-        <v>304014</v>
-      </c>
+      <c r="A39" s="6"/>
+      <c r="B39" s="5"/>
       <c r="D39" s="7"/>
       <c r="E39" s="5"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A40" s="6">
-        <v>45905</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C40">
-        <v>3631405</v>
-      </c>
+      <c r="A40" s="6"/>
+      <c r="B40" s="5"/>
       <c r="D40" s="7"/>
       <c r="E40" s="5"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A41" s="6">
-        <v>45906</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41">
-        <v>156504</v>
-      </c>
+      <c r="A41" s="6"/>
+      <c r="B41" s="5"/>
       <c r="D41" s="7"/>
       <c r="E41" s="5"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A42" s="6">
-        <v>45907</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C42">
-        <v>201031</v>
-      </c>
+      <c r="A42" s="6"/>
+      <c r="B42" s="5"/>
       <c r="D42" s="7"/>
       <c r="E42" s="5"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A43" s="6">
-        <v>45908</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C43">
-        <v>155404</v>
-      </c>
+      <c r="A43" s="6"/>
+      <c r="B43" s="5"/>
       <c r="D43" s="7"/>
       <c r="E43" s="5"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A44" s="6">
-        <v>45909</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C44">
-        <v>207485</v>
-      </c>
+      <c r="A44" s="6"/>
+      <c r="B44" s="5"/>
       <c r="D44" s="7"/>
       <c r="E44" s="5"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A45" s="6">
-        <v>45910</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C45">
-        <v>192730</v>
-      </c>
+      <c r="A45" s="6"/>
+      <c r="B45" s="5"/>
       <c r="D45" s="7"/>
       <c r="E45" s="5"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A46" s="6">
-        <v>45911</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C46">
-        <v>179898</v>
-      </c>
+      <c r="A46" s="6"/>
+      <c r="B46" s="5"/>
       <c r="D46" s="7"/>
       <c r="E46" s="5"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A47" s="6">
-        <v>45912</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C47">
-        <v>208708</v>
-      </c>
+      <c r="A47" s="6"/>
+      <c r="B47" s="5"/>
       <c r="D47" s="7"/>
       <c r="E47" s="5"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A48" s="6">
-        <v>45913</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C48">
-        <v>197926</v>
-      </c>
+      <c r="A48" s="6"/>
+      <c r="B48" s="5"/>
       <c r="D48" s="7"/>
       <c r="E48" s="5"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A49" s="6">
-        <v>45914</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C49">
-        <v>240309</v>
-      </c>
+      <c r="A49" s="6"/>
+      <c r="B49" s="5"/>
       <c r="D49" s="7"/>
       <c r="E49" s="5"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A50" s="6">
-        <v>45915</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C50">
-        <v>1719153</v>
-      </c>
+      <c r="A50" s="6"/>
+      <c r="B50" s="5"/>
       <c r="D50" s="7"/>
       <c r="E50" s="5"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A51" s="6">
-        <v>45916</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C51">
-        <v>236857</v>
-      </c>
+      <c r="A51" s="6"/>
+      <c r="B51" s="5"/>
       <c r="D51" s="7"/>
       <c r="E51" s="5"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A52" s="6">
-        <v>45917</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C52">
-        <v>250460</v>
-      </c>
+      <c r="A52" s="6"/>
+      <c r="B52" s="5"/>
       <c r="D52" s="7"/>
       <c r="E52" s="5"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A53" s="6">
-        <v>45918</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C53">
-        <v>184579</v>
-      </c>
+      <c r="A53" s="6"/>
+      <c r="B53" s="5"/>
       <c r="D53" s="7"/>
       <c r="E53" s="5"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A54" s="6">
-        <v>45919</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C54">
-        <v>128577</v>
-      </c>
+      <c r="A54" s="6"/>
+      <c r="B54" s="5"/>
       <c r="D54" s="7"/>
       <c r="E54" s="5"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A55" s="6">
-        <v>45920</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C55">
-        <v>288274</v>
-      </c>
+      <c r="A55" s="6"/>
+      <c r="B55" s="5"/>
       <c r="D55" s="7"/>
       <c r="E55" s="5"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A56" s="6">
-        <v>45921</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C56">
-        <v>269478</v>
-      </c>
+      <c r="A56" s="6"/>
+      <c r="B56" s="5"/>
       <c r="D56" s="7"/>
       <c r="E56" s="5"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A57" s="6">
-        <v>45922</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C57">
-        <v>167319</v>
-      </c>
+      <c r="A57" s="6"/>
+      <c r="B57" s="5"/>
       <c r="D57" s="7"/>
       <c r="E57" s="5"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A58" s="6">
-        <v>45923</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C58">
-        <v>111984</v>
-      </c>
+      <c r="A58" s="6"/>
+      <c r="B58" s="5"/>
       <c r="D58" s="7"/>
       <c r="E58" s="5"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A59" s="6">
-        <v>45924</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C59">
-        <v>87104</v>
-      </c>
+      <c r="A59" s="6"/>
+      <c r="B59" s="5"/>
       <c r="D59" s="7"/>
       <c r="E59" s="5"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A60" s="6">
-        <v>45925</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C60">
-        <v>1475309</v>
-      </c>
+      <c r="A60" s="6"/>
+      <c r="B60" s="5"/>
       <c r="D60" s="7"/>
       <c r="E60" s="5"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A61" s="6">
-        <v>45926</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C61">
-        <v>181648</v>
-      </c>
+      <c r="A61" s="6"/>
+      <c r="B61" s="5"/>
       <c r="D61" s="7"/>
       <c r="E61" s="5"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A62" s="6">
-        <v>45927</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C62">
-        <v>162168</v>
-      </c>
+      <c r="A62" s="6"/>
+      <c r="B62" s="5"/>
       <c r="D62" s="7"/>
       <c r="E62" s="5"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A63" s="6">
-        <v>45928</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C63">
-        <v>383611</v>
-      </c>
+      <c r="A63" s="6"/>
+      <c r="B63" s="5"/>
       <c r="D63" s="7"/>
       <c r="E63" s="5"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A64" s="6">
-        <v>45929</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C64">
-        <v>173493</v>
-      </c>
+      <c r="A64" s="6"/>
+      <c r="B64" s="5"/>
       <c r="D64" s="7"/>
       <c r="E64" s="5"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A65" s="6">
-        <v>45930</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C65">
-        <v>239144</v>
-      </c>
+      <c r="A65" s="6"/>
+      <c r="B65" s="5"/>
       <c r="D65" s="7"/>
       <c r="E65" s="5"/>
     </row>

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1721</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1722</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1768" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,8 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,7 +219,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -239,16 +240,16 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -262,18 +263,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -289,6 +298,14 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -316,25 +333,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +476,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,67 +500,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,79 +524,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,6 +572,32 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -586,17 +612,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,6 +639,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -633,202 +668,167 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1722"/>
+  <dimension ref="A1:E1723"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23231,8 +23231,19 @@
         <v>743847</v>
       </c>
     </row>
+    <row r="1723" spans="1:3">
+      <c r="A1723" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1723" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1723">
+        <v>278607</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1721">
+  <autoFilter ref="A1:E1722">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1722</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1723</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,9 +203,38 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,37 +248,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,6 +262,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -270,40 +284,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,15 +315,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,43 +398,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,19 +428,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,13 +446,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,49 +488,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +524,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,17 +586,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -615,8 +604,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -626,15 +630,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,17 +649,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1723"/>
+  <dimension ref="A1:E1724"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23242,8 +23242,19 @@
         <v>278607</v>
       </c>
     </row>
+    <row r="1724" spans="1:3">
+      <c r="A1724" s="1">
+        <v>46284</v>
+      </c>
+      <c r="B1724" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1724">
+        <v>790939</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1722">
+  <autoFilter ref="A1:E1723">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1723</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1724</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,37 +204,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,37 +225,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -293,7 +248,76 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -301,22 +325,6 @@
     <font>
       <b/>
       <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -333,15 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,25 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,37 +392,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +416,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,25 +434,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,13 +470,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,19 +482,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +512,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,6 +586,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -604,8 +624,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -625,15 +654,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -648,187 +668,167 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1724"/>
+  <dimension ref="A1:E1725"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23253,8 +23253,19 @@
         <v>790939</v>
       </c>
     </row>
+    <row r="1725" spans="1:3">
+      <c r="A1725" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B1725" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1725">
+        <v>729576</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1723">
+  <autoFilter ref="A1:E1724">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1724</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1725</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,20 +204,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -232,15 +218,15 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,54 +234,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -310,7 +249,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,10 +263,42 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -341,7 +312,36 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +392,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +452,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,19 +464,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,13 +482,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,31 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,43 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -588,53 +588,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,167 +624,211 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1725"/>
+  <dimension ref="A1:E1726"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23264,8 +23264,19 @@
         <v>729576</v>
       </c>
     </row>
+    <row r="1726" spans="1:3">
+      <c r="A1726" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1726" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1726">
+        <v>979752</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1724">
+  <autoFilter ref="A1:E1725">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1725</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1726</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,6 +203,36 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -218,10 +248,25 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -232,11 +277,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -248,15 +308,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -271,38 +325,6 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -312,36 +334,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,31 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,19 +392,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,43 +416,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,13 +434,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,43 +464,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -543,6 +477,72 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -589,8 +598,32 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -625,39 +658,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1726"/>
+  <dimension ref="A1:E1727"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23275,8 +23275,19 @@
         <v>979752</v>
       </c>
     </row>
+    <row r="1727" spans="1:3">
+      <c r="A1727" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1727" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1727">
+        <v>210918</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1725">
+  <autoFilter ref="A1:E1726">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1726</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1727</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,23 +203,24 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,6 +241,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -249,6 +265,21 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -256,7 +287,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -270,47 +315,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -326,7 +333,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -335,13 +342,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,6 +362,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -374,7 +410,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,43 +488,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,31 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,73 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,35 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -628,21 +610,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -654,6 +621,39 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,19 +674,19 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,127 +695,127 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1727"/>
+  <dimension ref="A1:E1728"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23286,8 +23286,19 @@
         <v>210918</v>
       </c>
     </row>
+    <row r="1728" spans="1:3">
+      <c r="A1728" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B1728" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1728">
+        <v>2480988</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1726">
+  <autoFilter ref="A1:E1727">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1727</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1728</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,31 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,14 +226,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -272,15 +249,16 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -301,15 +279,53 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,24 +340,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,31 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,13 +398,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,7 +422,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +476,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,19 +500,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,73 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,41 +571,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -629,16 +599,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,11 +621,50 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,152 +683,152 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1728"/>
+  <dimension ref="A1:E1729"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23297,8 +23297,19 @@
         <v>2480988</v>
       </c>
     </row>
+    <row r="1729" spans="1:3">
+      <c r="A1729" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B1729" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1729">
+        <v>221614</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1727">
+  <autoFilter ref="A1:E1728">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1728</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1729</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -217,11 +217,64 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -242,7 +295,31 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -256,16 +333,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,75 +342,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,61 +362,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,7 +404,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,7 +464,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,55 +512,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,32 +574,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -622,8 +598,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,6 +630,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -668,142 +659,142 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -812,10 +803,19 @@
     <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1729"/>
+  <dimension ref="A1:E1730"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23308,8 +23308,19 @@
         <v>221614</v>
       </c>
     </row>
+    <row r="1730" spans="1:3">
+      <c r="A1730" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B1730" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1730">
+        <v>11279734</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1728">
+  <autoFilter ref="A1:E1729">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1729</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1730</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -217,9 +217,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,8 +263,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,55 +317,10 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -317,9 +332,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -327,21 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +458,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,19 +470,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,79 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,31 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,15 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -598,8 +589,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -621,26 +612,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,167 +642,193 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1730"/>
+  <dimension ref="A1:E1731"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23319,8 +23319,19 @@
         <v>11279734</v>
       </c>
     </row>
+    <row r="1731" spans="1:3">
+      <c r="A1731" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B1731" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1731">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1729">
+  <autoFilter ref="A1:E1730">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1731</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1732</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,9 +164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -203,11 +203,17 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -220,7 +226,82 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -236,59 +317,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -302,31 +331,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -335,13 +342,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,6 +362,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -374,19 +404,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,91 +440,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,25 +464,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +488,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,6 +580,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -591,6 +600,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -621,39 +654,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,130 +692,130 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1732"/>
+  <dimension ref="A1:E1733"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23341,8 +23341,19 @@
         <v>1454784</v>
       </c>
     </row>
+    <row r="1733" spans="1:3">
+      <c r="A1733" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B1733" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1733">
+        <v>489839</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1731">
+  <autoFilter ref="A1:E1732">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1732</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1733</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -211,7 +211,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -232,40 +247,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -284,6 +278,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -292,42 +323,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -341,9 +341,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,19 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +386,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,13 +452,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,13 +494,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,97 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -590,30 +605,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -624,6 +615,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,17 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1733"/>
+  <dimension ref="A1:E1734"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23352,8 +23352,19 @@
         <v>489839</v>
       </c>
     </row>
+    <row r="1734" spans="1:3">
+      <c r="A1734" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B1734" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1734">
+        <v>749931</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1732">
+  <autoFilter ref="A1:E1733">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1733</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1734</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -167,8 +167,8 @@
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,8 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -224,9 +225,39 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,7 +272,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,15 +295,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,39 +308,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,18 +332,18 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,19 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,19 +374,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,13 +404,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,13 +446,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,25 +464,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,25 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,11 +586,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -598,8 +604,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,17 +625,31 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -648,42 +668,22 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,130 +692,130 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1734"/>
+  <dimension ref="A1:E1735"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23363,8 +23363,16 @@
         <v>749931</v>
       </c>
     </row>
+    <row r="1735" spans="1:2">
+      <c r="A1735" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B1735" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1733">
+  <autoFilter ref="A1:E1734">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1735</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1736</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,8 +165,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -205,6 +205,53 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -212,7 +259,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,30 +287,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -258,6 +298,13 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,46 +325,7 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -332,16 +340,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +398,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,97 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,31 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -591,6 +612,24 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -615,45 +654,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,130 +692,130 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1736"/>
+  <dimension ref="A1:E1737"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23385,8 +23385,19 @@
         <v>609537</v>
       </c>
     </row>
+    <row r="1737" spans="1:3">
+      <c r="A1737" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B1737" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1737">
+        <v>641335</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1735">
+  <autoFilter ref="A1:E1736">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1736</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1737</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -205,7 +205,38 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -220,53 +251,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -274,6 +259,13 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -289,36 +281,29 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,16 +317,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,19 +374,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,25 +428,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,25 +440,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,7 +482,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,13 +494,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,55 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,16 +572,25 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,35 +610,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -641,15 +626,6 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,167 +644,191 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1737"/>
+  <dimension ref="A1:E1738"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23396,8 +23396,19 @@
         <v>641335</v>
       </c>
     </row>
+    <row r="1738" spans="1:3">
+      <c r="A1738" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B1738" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1738">
+        <v>528722</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1736">
+  <autoFilter ref="A1:E1737">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1737</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1738</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,9 +203,97 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,51 +307,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -273,7 +317,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -288,28 +332,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -317,31 +339,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +404,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +476,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,49 +500,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,79 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -582,15 +591,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -630,6 +630,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -653,37 +668,22 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,143 +692,143 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1738"/>
+  <dimension ref="A1:E1739"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23407,8 +23407,19 @@
         <v>528722</v>
       </c>
     </row>
+    <row r="1739" spans="1:3">
+      <c r="A1739" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B1739" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1739">
+        <v>716217</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1737">
+  <autoFilter ref="A1:E1738">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1738</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1739</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1786" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,6 +204,44 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -211,7 +249,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,24 +279,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -256,60 +301,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,15 +317,22 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -341,7 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,19 +362,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,25 +398,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,55 +446,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,13 +464,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,7 +494,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,7 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,23 +574,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -610,37 +595,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -664,7 +629,42 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1739"/>
+  <dimension ref="A1:E1740"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23418,8 +23418,19 @@
         <v>716217</v>
       </c>
     </row>
+    <row r="1740" spans="1:3">
+      <c r="A1740" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B1740" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1740">
+        <v>3477547</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1738">
+  <autoFilter ref="A1:E1739">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1739</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1740</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1786" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,14 +204,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -219,7 +219,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,22 +227,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,15 +248,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,8 +270,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -295,7 +303,14 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,41 +324,26 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +416,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,91 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,67 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,6 +574,80 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -594,241 +668,167 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1740"/>
+  <dimension ref="A1:E1741"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23429,8 +23429,19 @@
         <v>3477547</v>
       </c>
     </row>
+    <row r="1741" spans="1:3">
+      <c r="A1741" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B1741" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1741">
+        <v>270784</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1739">
+  <autoFilter ref="A1:E1740">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1740</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1741</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,113 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -331,9 +225,61 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -344,6 +290,60 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,37 +446,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,7 +470,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,37 +500,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,67 +524,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -575,22 +575,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -611,16 +611,40 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -640,31 +664,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1741"/>
+  <dimension ref="A1:E1742"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23440,8 +23440,19 @@
         <v>270784</v>
       </c>
     </row>
+    <row r="1742" spans="1:3">
+      <c r="A1742" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B1742" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1742">
+        <v>303293</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1740">
+  <autoFilter ref="A1:E1741">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1741</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1742</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,35 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -240,8 +211,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -256,7 +257,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -269,9 +277,55 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -292,60 +346,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -362,67 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +386,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,13 +476,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,19 +500,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,55 +518,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,15 +567,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -610,32 +601,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -664,7 +634,37 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1742"/>
+  <dimension ref="A1:E1743"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23451,8 +23451,19 @@
         <v>303293</v>
       </c>
     </row>
+    <row r="1743" spans="1:3">
+      <c r="A1743" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B1743" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1743">
+        <v>1571948</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1741">
+  <autoFilter ref="A1:E1742">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1742</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1743</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,9 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -213,22 +213,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,30 +226,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,17 +250,31 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -301,16 +286,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,17 +318,32 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +434,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +446,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +482,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,109 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,45 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -586,17 +625,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -605,16 +644,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -634,37 +664,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,148 +674,148 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1743"/>
+  <dimension ref="A1:E1744"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23462,8 +23462,19 @@
         <v>1571948</v>
       </c>
     </row>
+    <row r="1744" spans="1:3">
+      <c r="A1744" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B1744" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1744">
+        <v>295477</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1742">
+  <autoFilter ref="A1:E1743">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1743</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1744</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,17 +203,8 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,17 +225,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -256,23 +241,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,13 +264,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -301,9 +272,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,15 +288,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -337,6 +314,29 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -362,13 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,73 +374,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,13 +410,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,13 +458,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +512,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,45 +567,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -649,13 +610,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,167 +642,193 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1744"/>
+  <dimension ref="A1:E1745"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23473,8 +23473,19 @@
         <v>295477</v>
       </c>
     </row>
+    <row r="1745" spans="1:3">
+      <c r="A1745" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B1745" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1745">
+        <v>741144</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1743">
+  <autoFilter ref="A1:E1744">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1744</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1745</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -217,9 +217,115 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -235,113 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,19 +422,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,13 +440,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +482,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,37 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,67 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,6 +572,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -582,6 +597,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -604,41 +643,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,17 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,19 +674,19 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,127 +695,127 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1745"/>
+  <dimension ref="A1:E1746"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23484,8 +23484,19 @@
         <v>741144</v>
       </c>
     </row>
+    <row r="1746" spans="1:3">
+      <c r="A1746" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B1746" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1746">
+        <v>568605</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1744">
+  <autoFilter ref="A1:E1745">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1745</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1746</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,58 +204,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -269,40 +225,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,6 +247,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -339,9 +279,69 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,19 +464,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,103 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,21 +572,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -597,6 +582,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,23 +628,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -643,8 +652,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -659,163 +668,154 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1746"/>
+  <dimension ref="A1:E1747"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23495,8 +23495,19 @@
         <v>568605</v>
       </c>
     </row>
+    <row r="1747" spans="1:3">
+      <c r="A1747" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B1747" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1747">
+        <v>1038261</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1745">
+  <autoFilter ref="A1:E1746">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1746</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1747</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -217,75 +217,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -301,8 +232,70 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -311,6 +304,20 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -325,23 +332,16 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,19 +392,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,13 +428,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +452,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,25 +476,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,67 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +524,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,32 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -582,15 +608,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -610,26 +627,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -652,19 +654,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,143 +692,143 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1747"/>
+  <dimension ref="A1:E1748"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23506,8 +23506,19 @@
         <v>1038261</v>
       </c>
     </row>
+    <row r="1748" spans="1:3">
+      <c r="A1748" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B1748" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1748">
+        <v>1038261</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1746">
+  <autoFilter ref="A1:E1747">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1747</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1748</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,37 +204,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -245,81 +222,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -339,9 +241,107 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,19 +464,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,19 +488,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,115 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,28 +571,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -612,17 +619,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -631,7 +634,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -650,31 +668,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,152 +683,152 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1748"/>
+  <dimension ref="A1:E1749"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23517,8 +23517,19 @@
         <v>1038261</v>
       </c>
     </row>
+    <row r="1749" spans="1:3">
+      <c r="A1749" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B1749" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1749">
+        <v>498306</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1747">
+  <autoFilter ref="A1:E1748">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1748</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1749</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,6 +204,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -211,36 +218,36 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -255,25 +262,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -284,33 +277,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -325,15 +317,15 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -342,6 +334,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,43 +500,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,7 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,115 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,20 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -604,37 +601,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,6 +625,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -668,167 +648,187 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1749"/>
+  <dimension ref="A1:E1750"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23528,8 +23528,19 @@
         <v>498306</v>
       </c>
     </row>
+    <row r="1750" spans="1:3">
+      <c r="A1750" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B1750" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1750">
+        <v>142255</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1748">
+  <autoFilter ref="A1:E1749">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1749</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1750</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,8 +203,24 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,15 +234,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,15 +249,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,6 +257,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -271,15 +279,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,14 +309,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -326,14 +318,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -342,6 +327,21 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,37 +380,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,85 +416,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,13 +434,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +512,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -582,6 +606,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -604,7 +637,18 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -624,96 +668,52 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -722,113 +722,113 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1750"/>
+  <dimension ref="A1:E1751"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23539,8 +23539,19 @@
         <v>142255</v>
       </c>
     </row>
+    <row r="1751" spans="1:3">
+      <c r="A1751" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B1751" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1751">
+        <v>5497033</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1749">
+  <autoFilter ref="A1:E1750">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1750</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1751</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,29 +203,21 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -234,29 +226,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,16 +249,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -300,9 +271,38 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,9 +316,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -326,7 +325,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -335,13 +342,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +380,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,133 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,24 +573,29 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -614,7 +619,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -634,22 +639,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,148 +674,148 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1751"/>
+  <dimension ref="A1:E1752"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23550,8 +23550,19 @@
         <v>5497033</v>
       </c>
     </row>
+    <row r="1752" spans="1:3">
+      <c r="A1752" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B1752" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1752">
+        <v>396958</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1750">
+  <autoFilter ref="A1:E1751">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1751</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1753</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,52 +204,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -272,12 +234,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -286,15 +249,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,17 +279,18 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -339,9 +310,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,19 +476,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,19 +500,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,127 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,29 +573,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -617,9 +597,50 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -639,32 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,148 +674,148 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1752"/>
+  <dimension ref="A1:E1754"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23561,8 +23561,30 @@
         <v>396958</v>
       </c>
     </row>
+    <row r="1753" spans="1:3">
+      <c r="A1753" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B1753" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1753">
+        <v>396958</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:3">
+      <c r="A1754" s="1">
+        <v>46312</v>
+      </c>
+      <c r="B1754" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1754">
+        <v>692322</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1751">
+  <autoFilter ref="A1:E1753">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1753</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1754</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,24 +204,24 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -240,7 +240,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -256,15 +255,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,39 +286,16 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,7 +317,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -341,7 +325,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +380,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +398,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +422,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,25 +470,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,25 +482,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,7 +494,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,25 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,7 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,15 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -591,6 +582,63 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -620,215 +668,167 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1754"/>
+  <dimension ref="A1:E1755"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23583,8 +23583,19 @@
         <v>692322</v>
       </c>
     </row>
+    <row r="1755" spans="1:3">
+      <c r="A1755" s="1">
+        <v>46313</v>
+      </c>
+      <c r="B1755" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1755">
+        <v>742182</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1753">
+  <autoFilter ref="A1:E1754">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1754</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1755</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -212,14 +220,36 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,28 +264,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -269,46 +286,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -325,7 +302,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,7 +310,23 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -342,6 +335,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,55 +404,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,19 +440,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,13 +482,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,61 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,17 +586,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -605,7 +601,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -638,18 +634,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1755"/>
+  <dimension ref="A1:E1756"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23594,8 +23594,19 @@
         <v>742182</v>
       </c>
     </row>
+    <row r="1756" spans="1:3">
+      <c r="A1756" s="1">
+        <v>46314</v>
+      </c>
+      <c r="B1756" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1756">
+        <v>106571</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1754">
+  <autoFilter ref="A1:E1755">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1755</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1756</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,6 +203,36 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -210,17 +240,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,90 +269,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -340,10 +285,65 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +416,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,19 +476,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,73 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,55 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,69 +571,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -654,6 +597,45 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -668,167 +650,185 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1756"/>
+  <dimension ref="A1:E1757"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23605,8 +23605,19 @@
         <v>106571</v>
       </c>
     </row>
+    <row r="1757" spans="1:3">
+      <c r="A1757" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B1757" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1757">
+        <v>445509</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1755">
+  <autoFilter ref="A1:E1756">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1756</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1757</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,6 +203,20 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,50 +234,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,15 +256,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -294,7 +264,7 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -309,9 +279,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -325,15 +294,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -344,6 +329,21 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,61 +470,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,73 +488,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,13 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -543,6 +531,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -597,11 +597,35 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -617,21 +641,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -659,176 +668,167 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1757"/>
+  <dimension ref="A1:E1758"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23616,8 +23616,19 @@
         <v>445509</v>
       </c>
     </row>
+    <row r="1758" spans="1:3">
+      <c r="A1758" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1758" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1758">
+        <v>497210</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1756">
+  <autoFilter ref="A1:E1757">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1757</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1758</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -233,8 +233,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -249,9 +250,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -264,23 +265,39 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -294,19 +311,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -324,24 +340,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,78 +362,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -446,7 +374,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,7 +500,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,43 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -624,23 +624,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -663,8 +648,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,148 +674,148 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1758"/>
+  <dimension ref="A1:E1759"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23627,8 +23627,19 @@
         <v>497210</v>
       </c>
     </row>
+    <row r="1759" spans="1:3">
+      <c r="A1759" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1759" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1759">
+        <v>641345</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1757">
+  <autoFilter ref="A1:E1758">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1758</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1759</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,25 +203,11 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -242,6 +228,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -256,50 +257,47 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -320,21 +318,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -342,6 +334,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,31 +404,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,73 +416,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,13 +440,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,25 +494,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,10 +573,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -593,6 +591,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -616,16 +638,18 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -644,178 +668,154 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1759"/>
+  <dimension ref="A1:E1760"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23638,8 +23638,19 @@
         <v>641345</v>
       </c>
     </row>
+    <row r="1760" spans="1:3">
+      <c r="A1760" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1760" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1760">
+        <v>190000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1758">
+  <autoFilter ref="A1:E1759">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1759</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1761</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -166,8 +166,8 @@
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
@@ -203,6 +203,90 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -219,6 +303,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -228,66 +319,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -301,47 +340,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,25 +470,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,121 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,54 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -637,8 +589,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,13 +620,61 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,130 +692,130 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1760"/>
+  <dimension ref="A1:E1762"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23649,8 +23649,30 @@
         <v>190000</v>
       </c>
     </row>
+    <row r="1761" spans="1:3">
+      <c r="A1761" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1761" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1761">
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:3">
+      <c r="A1762" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B1762" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1762">
+        <v>148325</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1759">
+  <autoFilter ref="A1:E1761">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1761</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1762</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -210,8 +210,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -226,17 +250,10 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -248,40 +265,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -292,6 +277,21 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -310,9 +310,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -320,28 +342,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,37 +416,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,13 +458,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,43 +488,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,31 +512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -582,6 +606,36 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -606,65 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,143 +692,143 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1762"/>
+  <dimension ref="A1:E1763"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23671,8 +23671,19 @@
         <v>148325</v>
       </c>
     </row>
+    <row r="1763" spans="1:3">
+      <c r="A1763" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B1763" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1763">
+        <v>16281020</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1761">
+  <autoFilter ref="A1:E1762">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1762</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1763</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,7 +204,45 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,38 +257,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -265,8 +272,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -280,31 +295,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,8 +309,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,9 +333,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +380,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +392,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +494,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,67 +512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,67 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,30 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -606,21 +582,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -643,8 +604,56 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -659,163 +668,154 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1763"/>
+  <dimension ref="A1:E1764"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23682,8 +23682,19 @@
         <v>16281020</v>
       </c>
     </row>
+    <row r="1764" spans="1:3">
+      <c r="A1764" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1764" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1764">
+        <v>368684</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1762">
+  <autoFilter ref="A1:E1763">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1763</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1764</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,6 +204,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -211,7 +218,82 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,85 +307,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -319,7 +325,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -328,20 +342,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +398,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,13 +422,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,25 +452,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +470,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,13 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,73 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,41 +586,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -649,11 +619,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,167 +659,176 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1764"/>
+  <dimension ref="A1:E1765"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23693,8 +23693,19 @@
         <v>368684</v>
       </c>
     </row>
+    <row r="1765" spans="1:3">
+      <c r="A1765" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1765" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1765">
+        <v>442833</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1763">
+  <autoFilter ref="A1:E1764">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1764</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1765</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,6 +203,53 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -217,15 +264,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -246,46 +309,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -307,41 +332,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,43 +410,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,103 +440,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -543,6 +453,96 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -590,6 +599,47 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -618,72 +668,22 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,143 +692,143 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1765"/>
+  <dimension ref="A1:E1766"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23704,8 +23704,19 @@
         <v>442833</v>
       </c>
     </row>
+    <row r="1766" spans="1:3">
+      <c r="A1766" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1766" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1766">
+        <v>509634</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1764">
+  <autoFilter ref="A1:E1765">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1765</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1766</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,6 +203,20 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -212,39 +226,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,23 +246,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -294,16 +269,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,6 +292,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -332,18 +308,42 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +464,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,19 +488,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,127 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,6 +580,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -591,6 +600,32 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,202 +668,167 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1766"/>
+  <dimension ref="A1:E1767"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23715,8 +23715,19 @@
         <v>509634</v>
       </c>
     </row>
+    <row r="1767" spans="1:3">
+      <c r="A1767" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1767" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1767">
+        <v>765451</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1765">
+  <autoFilter ref="A1:E1766">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/winecom.xlsx
+++ b/dashboard/data/incoming/winecom.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1766</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1767</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,50 +204,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -255,38 +211,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -297,22 +222,6 @@
       <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -332,8 +241,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -344,6 +291,59 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +422,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +440,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,151 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -583,8 +589,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -615,6 +636,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -629,206 +668,167 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1767"/>
+  <dimension ref="A1:E1768"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23726,8 +23726,19 @@
         <v>765451</v>
       </c>
     </row>
+    <row r="1768" spans="1:3">
+      <c r="A1768" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1768" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1768">
+        <v>463340</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1766">
+  <autoFilter ref="A1:E1767">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
